--- a/SteadyShear.xlsx
+++ b/SteadyShear.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alain\Documents\VS Code\BIEN-514\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D43A991E-0BD9-4967-B1FA-38AFD98F70A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F963C8-F8D7-454F-8CF7-92295E95A9FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11460" yWindow="4035" windowWidth="28800" windowHeight="15285" activeTab="2" xr2:uid="{D38CB81E-1DC6-43BA-8BE9-97DCFA402144}"/>
+    <workbookView xWindow="15300" yWindow="2700" windowWidth="28800" windowHeight="15285" activeTab="2" xr2:uid="{D38CB81E-1DC6-43BA-8BE9-97DCFA402144}"/>
   </bookViews>
   <sheets>
     <sheet name="640 kDa" sheetId="1" r:id="rId1"/>
@@ -431,7 +431,7 @@
         <v>9.5469747032875304E-3</v>
       </c>
       <c r="B2">
-        <v>4.9867498681267097</v>
+        <v>1.7273530128855701</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -439,7 +439,7 @@
         <v>1.1492187010037E-2</v>
       </c>
       <c r="B3">
-        <v>5.2419984200455199</v>
+        <v>1.83398704204186</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -447,7 +447,7 @@
         <v>1.47158460192805E-2</v>
       </c>
       <c r="B4">
-        <v>5.1574069024354703</v>
+        <v>1.79852995951745</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -455,7 +455,7 @@
         <v>1.8270270041765398E-2</v>
       </c>
       <c r="B5">
-        <v>4.99063225891791</v>
+        <v>1.72896691731857</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -463,7 +463,7 @@
         <v>2.4887034759027898E-2</v>
       </c>
       <c r="B6">
-        <v>4.82978752438438</v>
+        <v>1.66231617377179</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -471,7 +471,7 @@
         <v>2.8600645757603901E-2</v>
       </c>
       <c r="B7">
-        <v>4.8305930328658304</v>
+        <v>1.6626488671917701</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -479,7 +479,7 @@
         <v>3.7772976464674597E-2</v>
       </c>
       <c r="B8">
-        <v>4.7528166042419802</v>
+        <v>1.6305768340762301</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -487,7 +487,7 @@
         <v>4.9121901258538603E-2</v>
       </c>
       <c r="B9">
-        <v>4.75431398328685</v>
+        <v>1.63119331109231</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -495,7 +495,7 @@
         <v>6.0986667010688903E-2</v>
       </c>
       <c r="B10">
-        <v>4.67741901511575</v>
+        <v>1.59958577094793</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -503,7 +503,7 @@
         <v>7.3412803970701296E-2</v>
       </c>
       <c r="B11">
-        <v>4.7566050049514397</v>
+        <v>1.6321366091468901</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -511,7 +511,7 @@
         <v>9.2564178897127994E-2</v>
       </c>
       <c r="B12">
-        <v>4.6797596951632201</v>
+        <v>1.6005463791358601</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -519,7 +519,7 @@
         <v>0.12224984640507799</v>
       </c>
       <c r="B13">
-        <v>4.8390141546819496</v>
+        <v>1.6661276471087201</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -527,7 +527,7 @@
         <v>0.15177773017322699</v>
       </c>
       <c r="B14">
-        <v>4.6825353513045496</v>
+        <v>1.60168562477197</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -535,7 +535,7 @@
         <v>0.19137235207582501</v>
       </c>
       <c r="B15">
-        <v>4.7620726666604698</v>
+        <v>1.6343882141428501</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -543,7 +543,7 @@
         <v>0.24129611832536099</v>
       </c>
       <c r="B16">
-        <v>4.6081673000432204</v>
+        <v>1.57120873681785</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -551,7 +551,7 @@
         <v>0.28600645757603899</v>
       </c>
       <c r="B17">
-        <v>4.7643674271003702</v>
+        <v>1.6353333597686499</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -559,7 +559,7 @@
         <v>0.38361238274175402</v>
       </c>
       <c r="B18">
-        <v>4.8456538746650502</v>
+        <v>1.6688713807828699</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -567,7 +567,7 @@
         <v>0.44772022300821301</v>
       </c>
       <c r="B19">
-        <v>4.7669282721710697</v>
+        <v>1.6363882054751</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -575,7 +575,7 @@
         <v>0.61936449909706204</v>
       </c>
       <c r="B20">
-        <v>4.4630384774601</v>
+        <v>1.5120172896661901</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -583,7 +583,7 @@
         <v>0.74556106748143802</v>
       </c>
       <c r="B21">
-        <v>4.5385951291884004</v>
+        <v>1.54278614935716</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -591,7 +591,7 @@
         <v>0.94005737822829905</v>
       </c>
       <c r="B22">
-        <v>4.5398567720280001</v>
+        <v>1.5433008017937999</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -599,7 +599,7 @@
         <v>1.1492187010037</v>
       </c>
       <c r="B23">
-        <v>4.5409504795063604</v>
+        <v>1.54374697277438</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -607,7 +607,7 @@
         <v>1.4490181504862001</v>
       </c>
       <c r="B24">
-        <v>4.5422127770883902</v>
+        <v>1.54426194572862</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -615,7 +615,7 @@
         <v>1.88437695865931</v>
       </c>
       <c r="B25">
-        <v>4.5436438052125698</v>
+        <v>1.5448457894190699</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -623,7 +623,7 @@
         <v>2.3759589128427701</v>
       </c>
       <c r="B26">
-        <v>4.5449068514877604</v>
+        <v>1.54536112892357</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -631,7 +631,7 @@
         <v>2.9498413403416999</v>
       </c>
       <c r="B27">
-        <v>4.5460860114486898</v>
+        <v>1.54584226756119</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -639,7 +639,7 @@
         <v>3.7193735530726402</v>
       </c>
       <c r="B28">
-        <v>4.2558016504376797</v>
+        <v>1.4281625953408299</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -647,7 +647,7 @@
         <v>4.7626903780279903</v>
       </c>
       <c r="B29">
-        <v>4.2570635625548796</v>
+        <v>1.42867077761061</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -655,7 +655,7 @@
         <v>5.9130572049939998</v>
       </c>
       <c r="B30">
-        <v>4.3292936146886003</v>
+        <v>1.45780840234966</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -663,7 +663,7 @@
         <v>7.11785265100134</v>
       </c>
       <c r="B31">
-        <v>4.1203193146235</v>
+        <v>1.3737795553910801</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -671,7 +671,7 @@
         <v>9.4005737822830007</v>
       </c>
       <c r="B32">
-        <v>4.1216937970013099</v>
+        <v>1.37432950270216</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -679,7 +679,7 @@
         <v>11.6711619111007</v>
       </c>
       <c r="B33">
-        <v>3.9884109231294</v>
+        <v>1.32117356794237</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -687,7 +687,7 @@
         <v>14.267977510008601</v>
       </c>
       <c r="B34">
-        <v>3.7335978077480698</v>
+        <v>1.2205428739089701</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -695,7 +695,7 @@
         <v>18.2702700417654</v>
       </c>
       <c r="B35">
-        <v>3.553641026397</v>
+        <v>1.1502924416590199</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -703,7 +703,7 @@
         <v>23.395240647448301</v>
       </c>
       <c r="B36">
-        <v>3.3823580349991702</v>
+        <v>1.08408539316626</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -711,7 +711,7 @@
         <v>30.898179077880201</v>
       </c>
       <c r="B37">
-        <v>3.2194500702942399</v>
+        <v>1.0217344408673501</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -719,7 +719,7 @@
         <v>37.1937355307264</v>
       </c>
       <c r="B38">
-        <v>3.0640477379711002</v>
+        <v>0.96284112757215601</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -727,7 +727,7 @@
         <v>46.896554869265501</v>
       </c>
       <c r="B39">
-        <v>3.0145465291498499</v>
+        <v>0.94420520425935095</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -735,7 +735,7 @@
         <v>58.223816718886702</v>
       </c>
       <c r="B40">
-        <v>2.8691411829504601</v>
+        <v>0.88982028725685203</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -743,7 +743,7 @@
         <v>74.556106748143904</v>
       </c>
       <c r="B41">
-        <v>2.5137768274357399</v>
+        <v>0.75926269510727495</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -751,7 +751,7 @@
         <v>94.00573782283</v>
       </c>
       <c r="B42">
-        <v>2.4325341057677101</v>
+        <v>0.72991237318611202</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -759,7 +759,7 @@
         <v>116.711619111007</v>
       </c>
       <c r="B43">
-        <v>2.0961550232991102</v>
+        <v>0.61053150255212596</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -767,7 +767,7 @@
         <v>151.77773017322701</v>
       </c>
       <c r="B44">
-        <v>1.99515879833653</v>
+        <v>0.57540411209557196</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -775,7 +775,7 @@
         <v>188.437695865931</v>
       </c>
       <c r="B45">
-        <v>1.7479788455816301</v>
+        <v>0.49095694388808597</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -783,7 +783,7 @@
         <v>233.95240647448199</v>
       </c>
       <c r="B46">
-        <v>1.6094504510651</v>
+        <v>0.44464471337572298</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -791,7 +791,7 @@
         <v>294.98413403417101</v>
       </c>
       <c r="B47">
-        <v>1.4819279758008601</v>
+        <v>0.40271009459542201</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -799,7 +799,7 @@
         <v>371.937355307264</v>
       </c>
       <c r="B48">
-        <v>1.3200430450959499</v>
+        <v>0.35051427682044201</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -807,7 +807,7 @@
         <v>483.68626864371799</v>
       </c>
       <c r="B49">
-        <v>1.13756624079858</v>
+        <v>0.293205447047796</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -815,7 +815,7 @@
         <v>591.30572049939894</v>
       </c>
       <c r="B50">
-        <v>1.01326163008742</v>
+        <v>0.25519133076648098</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -823,7 +823,7 @@
         <v>745.56106748143895</v>
       </c>
       <c r="B51">
-        <v>0.91764951285893204</v>
+        <v>0.226575113424135</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -831,7 +831,7 @@
         <v>954.69747032875296</v>
       </c>
       <c r="B52">
-        <v>0.83107482501163699</v>
+        <v>0.201172286548886</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -839,7 +839,7 @@
         <v>1185.2924098446999</v>
       </c>
       <c r="B53">
-        <v>0.71615097402129602</v>
+        <v>0.16826953876999301</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -847,7 +847,7 @@
         <v>1494.50249460652</v>
       </c>
       <c r="B54">
-        <v>0.61713061869132202</v>
+        <v>0.14075133189282599</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -855,7 +855,7 @@
         <v>1855.4804201388399</v>
       </c>
       <c r="B55">
-        <v>0.55888736084363899</v>
+        <v>0.124965216480102</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -863,7 +863,7 @@
         <v>2450.5397127942601</v>
       </c>
       <c r="B56">
-        <v>0.47372542353619201</v>
+        <v>0.10247832806790901</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -871,7 +871,7 @@
         <v>3089.81790778802</v>
       </c>
       <c r="B57">
-        <v>0.41504333557385098</v>
+        <v>8.7440399597959698E-2</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -879,7 +879,7 @@
         <v>3895.8661446875599</v>
       </c>
       <c r="B58">
-        <v>0.35765635984289501</v>
+        <v>7.3140705053435506E-2</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -887,7 +887,7 @@
         <v>4988.6906858441198</v>
       </c>
       <c r="B59">
-        <v>0.313357974470094</v>
+        <v>6.2409241097565397E-2</v>
       </c>
     </row>
   </sheetData>
@@ -913,7 +913,7 @@
         <v>1.0155736154404099E-2</v>
       </c>
       <c r="B2">
-        <v>21.783995752715601</v>
+        <v>10.133630213321</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -921,7 +921,7 @@
         <v>1.2224984640507801E-2</v>
       </c>
       <c r="B3">
-        <v>22.899017263304099</v>
+        <v>10.7592057682686</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -929,7 +929,7 @@
         <v>1.5654199796841298E-2</v>
       </c>
       <c r="B4">
-        <v>24.8838069606504</v>
+        <v>11.8877643713864</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -937,7 +937,7 @@
         <v>1.9137235207582499E-2</v>
       </c>
       <c r="B5">
-        <v>24.889801776594901</v>
+        <v>11.891201145008401</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -945,7 +945,7 @@
         <v>2.4887034759027898E-2</v>
       </c>
       <c r="B6">
-        <v>24.0862811823119</v>
+        <v>11.432039131999099</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -953,7 +953,7 @@
         <v>3.1379375436648302E-2</v>
       </c>
       <c r="B7">
-        <v>24.495409570763901</v>
+        <v>11.665454026672201</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -961,7 +961,7 @@
         <v>3.8361238274175397E-2</v>
       </c>
       <c r="B8">
-        <v>24.910564216913802</v>
+        <v>11.903105343203199</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -969,7 +969,7 @@
         <v>4.9886906858441202E-2</v>
       </c>
       <c r="B9">
-        <v>24.509029976476601</v>
+        <v>11.673238197810299</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -977,7 +977,7 @@
         <v>6.1936449909706197E-2</v>
       </c>
       <c r="B10">
-        <v>24.9248773057294</v>
+        <v>11.9113129449303</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -985,7 +985,7 @@
         <v>7.6896405670187296E-2</v>
       </c>
       <c r="B11">
-        <v>24.5217491880178</v>
+        <v>11.6805081105068</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -993,7 +993,7 @@
         <v>9.69565561593594E-2</v>
       </c>
       <c r="B12">
-        <v>24.528565766363499</v>
+        <v>11.684404568848</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1001,7 +1001,7 @@
         <v>0.12608724076806799</v>
       </c>
       <c r="B13">
-        <v>24.536293512547999</v>
+        <v>11.688822126311599</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1009,7 +1009,7 @@
         <v>0.156541997968413</v>
       </c>
       <c r="B14">
-        <v>24.542659366864701</v>
+        <v>11.6924613688472</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1017,7 +1017,7 @@
         <v>0.20045339809052401</v>
       </c>
       <c r="B15">
-        <v>24.960002264455799</v>
+        <v>11.9314587602969</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1025,7 +1025,7 @@
         <v>0.24887034759027901</v>
       </c>
       <c r="B16">
-        <v>23.365781089809101</v>
+        <v>11.022912608071101</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1033,7 +1033,7 @@
         <v>0.308981790778802</v>
       </c>
       <c r="B17">
-        <v>22.987869365949599</v>
+        <v>10.809322256517699</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1041,7 +1041,7 @@
         <v>0.408073370441216</v>
       </c>
       <c r="B18">
-        <v>23.379639787264399</v>
+        <v>11.0307585569605</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1049,7 +1049,7 @@
         <v>0.468965548692655</v>
       </c>
       <c r="B19">
-        <v>21.8843303786043</v>
+        <v>10.189665207413499</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1057,7 +1057,7 @@
         <v>0.63880620726572201</v>
       </c>
       <c r="B20">
-        <v>22.258118600866901</v>
+        <v>10.3988698482007</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -1065,7 +1065,7 @@
         <v>0.76896405670187196</v>
       </c>
       <c r="B21">
-        <v>21.897310398940999</v>
+        <v>10.196918062921</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1073,7 +1073,7 @@
         <v>0.96956556159359397</v>
       </c>
       <c r="B22">
-        <v>20.841489294324401</v>
+        <v>9.6098033269307006</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1081,7 +1081,7 @@
         <v>1.20375169802007</v>
       </c>
       <c r="B23">
-        <v>21.1951090691182</v>
+        <v>9.80579448706664</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1089,7 +1089,7 @@
         <v>1.51777730173227</v>
       </c>
       <c r="B24">
-        <v>19.515745302311402</v>
+        <v>8.88100613069264</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1097,7 +1097,7 @@
         <v>2.0357518222611102</v>
       </c>
       <c r="B25">
-        <v>19.201881922117099</v>
+        <v>8.7098876639172698</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1105,7 +1105,7 @@
         <v>2.4887034759027902</v>
       </c>
       <c r="B26">
-        <v>18.275348828200201</v>
+        <v>8.2080276412356792</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1113,7 +1113,7 @@
         <v>3.1868065762459099</v>
       </c>
       <c r="B27">
-        <v>17.108717405910198</v>
+        <v>7.5833472532355497</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1121,7 +1121,7 @@
         <v>3.89586614468756</v>
       </c>
       <c r="B28">
-        <v>16.555167454407599</v>
+        <v>7.2898785595470699</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1129,7 +1129,7 @@
         <v>4.83686268643718</v>
       </c>
       <c r="B29">
-        <v>15.497771776875</v>
+        <v>6.7347753447156196</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -1137,7 +1137,7 @@
         <v>6.0986667010689004</v>
       </c>
       <c r="B30">
-        <v>15.247397597816301</v>
+        <v>6.6044228356058596</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -1145,7 +1145,7 @@
         <v>7.5717214883374098</v>
       </c>
       <c r="B31">
-        <v>13.358399578708401</v>
+        <v>5.6351478610482797</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -1153,7 +1153,7 @@
         <v>10.155736154404201</v>
       </c>
       <c r="B32">
-        <v>12.9276277644208</v>
+        <v>5.4177954776537902</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -1161,7 +1161,7 @@
         <v>12.6087240768068</v>
       </c>
       <c r="B33">
-        <v>11.9031053432031</v>
+        <v>4.9067319390817898</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -1169,7 +1169,7 @@
         <v>15.897992284504801</v>
       </c>
       <c r="B34">
-        <v>10.428624472911601</v>
+        <v>4.1867057119537003</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -1177,7 +1177,7 @@
         <v>19.7379485881577</v>
       </c>
       <c r="B35">
-        <v>9.6021495937105499</v>
+        <v>3.7917715279417799</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1185,7 +1185,7 @@
         <v>24.505397127942601</v>
       </c>
       <c r="B36">
-        <v>8.9888503623151408</v>
+        <v>3.50303906856352</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1193,7 +1193,7 @@
         <v>32.364366763473598</v>
       </c>
       <c r="B37">
-        <v>7.8758066277996699</v>
+        <v>2.9891936664938199</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -1201,7 +1201,7 @@
         <v>40.181564806037997</v>
       </c>
       <c r="B38">
-        <v>7.1325075233829001</v>
+        <v>2.65393746979804</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -1209,7 +1209,7 @@
         <v>50.663826361366702</v>
       </c>
       <c r="B39">
-        <v>6.2489779235677103</v>
+        <v>2.2644919881338899</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -1217,7 +1217,7 @@
         <v>61.936449909706297</v>
       </c>
       <c r="B40">
-        <v>5.3847482432589899</v>
+        <v>1.8940807222529601</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -1225,7 +1225,7 @@
         <v>78.093960720845203</v>
       </c>
       <c r="B41">
-        <v>4.87663941431222</v>
+        <v>1.68168547571719</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -1233,7 +1233,7 @@
         <v>98.466520279412507</v>
       </c>
       <c r="B42">
-        <v>4.1333188359614299</v>
+        <v>1.3789822898953701</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -1241,7 +1241,7 @@
         <v>124.15371850064101</v>
       </c>
       <c r="B43">
-        <v>3.6817975445981999</v>
+        <v>1.20025046945114</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -1249,7 +1249,7 @@
         <v>163.97026580002</v>
       </c>
       <c r="B44">
-        <v>3.1207739222380901</v>
+        <v>0.984271182306656</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -1257,7 +1257,7 @@
         <v>203.575182226111</v>
       </c>
       <c r="B45">
-        <v>2.7798109260978499</v>
+        <v>0.85667937095454505</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -1265,7 +1265,7 @@
         <v>248.87034759027901</v>
       </c>
       <c r="B46">
-        <v>2.3953648394954699</v>
+        <v>0.71654918197081097</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -1273,7 +1273,7 @@
         <v>308.98179077880201</v>
       </c>
       <c r="B47">
-        <v>2.0986034146149599</v>
+        <v>0.61138735217705098</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -1281,7 +1281,7 @@
         <v>383.612382741754</v>
       </c>
       <c r="B48">
-        <v>1.74946938159525</v>
+        <v>0.49145936511229699</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -1289,7 +1289,7 @@
         <v>514.52845309858606</v>
       </c>
       <c r="B49">
-        <v>1.53286986721125</v>
+        <v>0.41937867617638502</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -1297,7 +1297,7 @@
         <v>629.01024362344594</v>
       </c>
       <c r="B50">
-        <v>1.3429379432141599</v>
+        <v>0.35782207793510501</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -1305,7 +1305,7 @@
         <v>757.17214883374095</v>
       </c>
       <c r="B51">
-        <v>1.1381776820748799</v>
+        <v>0.293394574545915</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -1313,7 +1313,7 @@
         <v>1000</v>
       </c>
       <c r="B52">
-        <v>0.96474485249848396</v>
+        <v>0.24059963492679901</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -1321,7 +1321,7 @@
         <v>1260.87240768068</v>
       </c>
       <c r="B53">
-        <v>0.83135206024861596</v>
+        <v>0.20125281923523899</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -1329,7 +1329,7 @@
         <v>1565.4199796841301</v>
       </c>
       <c r="B54">
-        <v>0.70462036799923999</v>
+        <v>0.16502366627925899</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -1337,7 +1337,7 @@
         <v>1943.5271149298301</v>
       </c>
       <c r="B55">
-        <v>0.60718306904656105</v>
+        <v>0.138033208685513</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -1345,7 +1345,7 @@
         <v>2375.9589128427701</v>
       </c>
       <c r="B56">
-        <v>0.50615971469027099</v>
+        <v>0.110954543764562</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -1353,7 +1353,7 @@
         <v>2904.6061215980499</v>
       </c>
       <c r="B57">
-        <v>0.45838112200616099</v>
+        <v>9.8508128443088303E-2</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -1361,7 +1361,7 @@
         <v>4144.2854818394198</v>
       </c>
       <c r="B58">
-        <v>0.35768286957919199</v>
+        <v>7.3147210589114497E-2</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -1369,7 +1369,7 @@
         <v>5225.4152136029797</v>
       </c>
       <c r="B59">
-        <v>0.31337539404074799</v>
+        <v>6.2413404316567299E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1395,7 +1395,7 @@
         <v>9.8466520279412491E-3</v>
       </c>
       <c r="B2">
-        <v>153.83045069903901</v>
+        <v>105.79149999674</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1403,7 +1403,7 @@
         <v>1.1852924098447E-2</v>
       </c>
       <c r="B3">
-        <v>172.782037776469</v>
+        <v>121.61812682422899</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1411,7 +1411,7 @@
         <v>1.5177773017322699E-2</v>
       </c>
       <c r="B4">
-        <v>178.655272214619</v>
+        <v>126.595714540298</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1419,7 +1419,7 @@
         <v>1.88437695865931E-2</v>
       </c>
       <c r="B5">
-        <v>181.68653529923299</v>
+        <v>129.177623879842</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1427,7 +1427,7 @@
         <v>2.4887034759027898E-2</v>
       </c>
       <c r="B6">
-        <v>175.824383984793</v>
+        <v>124.192372993663</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1435,7 +1435,7 @@
         <v>3.1379375436648302E-2</v>
       </c>
       <c r="B7">
-        <v>181.79766568940201</v>
+        <v>129.27244502428201</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1443,7 +1443,7 @@
         <v>3.7193735530726503E-2</v>
       </c>
       <c r="B8">
-        <v>173.019115890373</v>
+        <v>121.81840424627001</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1451,7 +1451,7 @@
         <v>4.9121901258538603E-2</v>
       </c>
       <c r="B9">
-        <v>181.89538184231699</v>
+        <v>129.355830153547</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1459,7 +1459,7 @@
         <v>6.4875472947863E-2</v>
       </c>
       <c r="B10">
-        <v>176.02649205364199</v>
+        <v>124.363701892191</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1467,7 +1467,7 @@
         <v>7.9310166033330604E-2</v>
       </c>
       <c r="B11">
-        <v>170.33118165557499</v>
+        <v>119.55093888427299</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1475,7 +1475,7 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>173.224418736318</v>
+        <v>121.991883101271</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1483,7 +1483,7 @@
         <v>0.12608724076806799</v>
       </c>
       <c r="B13">
-        <v>159.49923282652699</v>
+        <v>110.48678035686901</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1491,7 +1491,7 @@
         <v>0.15414145817536401</v>
       </c>
       <c r="B14">
-        <v>162.202467788734</v>
+        <v>112.737642496571</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1499,7 +1499,7 @@
         <v>0.197379485881577</v>
       </c>
       <c r="B15">
-        <v>154.384423228636</v>
+        <v>106.248834700038</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1507,7 +1507,7 @@
         <v>0.24129611832536099</v>
       </c>
       <c r="B16">
-        <v>144.52105242571699</v>
+        <v>98.156109992597294</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1515,7 +1515,7 @@
         <v>0.299578103498643</v>
       </c>
       <c r="B17">
-        <v>130.88151378363901</v>
+        <v>87.147307020935401</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1523,7 +1523,7 @@
         <v>0.38958661446875598</v>
       </c>
       <c r="B18">
-        <v>135.332966590209</v>
+        <v>90.716089819174002</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1531,7 +1531,7 @@
         <v>0.476269037802799</v>
       </c>
       <c r="B19">
-        <v>122.55830574743</v>
+        <v>80.5399393712445</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1539,7 +1539,7 @@
         <v>0.600514488398177</v>
       </c>
       <c r="B20">
-        <v>116.64892037558801</v>
+        <v>75.902637693537301</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -1547,7 +1547,7 @@
         <v>0.76896405670187196</v>
       </c>
       <c r="B21">
-        <v>103.90818703775101</v>
+        <v>66.066259810686205</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1555,7 +1555,7 @@
         <v>1</v>
       </c>
       <c r="B22">
-        <v>95.678718033962099</v>
+        <v>59.838185708807003</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1563,7 +1563,7 @@
         <v>1.20375169802007</v>
       </c>
       <c r="B23">
-        <v>86.645586769636793</v>
+        <v>53.124607767695501</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1571,7 +1571,7 @@
         <v>1.54141458175364</v>
       </c>
       <c r="B24">
-        <v>82.469330590950307</v>
+        <v>50.066930123945802</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1579,7 +1579,7 @@
         <v>1.88437695865931</v>
       </c>
       <c r="B25">
-        <v>73.457707647989594</v>
+        <v>43.575747498440698</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1587,7 +1587,7 @@
         <v>2.4887034759027902</v>
       </c>
       <c r="B26">
-        <v>67.641152545949296</v>
+        <v>39.468734236643002</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1595,7 +1595,7 @@
         <v>3.0424361767689998</v>
       </c>
       <c r="B27">
-        <v>59.2600012693539</v>
+        <v>33.675494965042397</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1603,7 +1603,7 @@
         <v>3.83612382741754</v>
       </c>
       <c r="B28">
-        <v>51.919249782599501</v>
+        <v>28.733867852050398</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1611,7 +1611,7 @@
         <v>4.83686268643718</v>
       </c>
       <c r="B29">
-        <v>46.247621815144001</v>
+        <v>25.009631110771899</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -1619,7 +1619,7 @@
         <v>6.00514488398177</v>
       </c>
       <c r="B30">
-        <v>39.197612973655602</v>
+        <v>20.5074444863663</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -1627,7 +1627,7 @@
         <v>7.8093960720845201</v>
       </c>
       <c r="B31">
-        <v>33.779111525471599</v>
+        <v>17.154492202076899</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -1635,7 +1635,7 @@
         <v>9.8466520279412499</v>
       </c>
       <c r="B32">
-        <v>31.622190653319699</v>
+        <v>15.8485795214565</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -1643,7 +1643,7 @@
         <v>12.8050874967733</v>
       </c>
       <c r="B33">
-        <v>27.706061839293699</v>
+        <v>13.5235203557215</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -1651,7 +1651,7 @@
         <v>15.1777730173227</v>
       </c>
       <c r="B34">
-        <v>22.342827841286599</v>
+        <v>10.4463787298741</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -1659,7 +1659,7 @@
         <v>18.843769586593101</v>
       </c>
       <c r="B35">
-        <v>19.253185681209199</v>
+        <v>8.7378205062327492</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1667,7 +1667,7 @@
         <v>24.887034759027902</v>
       </c>
       <c r="B36">
-        <v>17.1509324955464</v>
+        <v>7.60580672456316</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1675,7 +1675,7 @@
         <v>32.364366763473598</v>
       </c>
       <c r="B37">
-        <v>15.0269410975573</v>
+        <v>6.4900000610187201</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -1683,7 +1683,7 @@
         <v>40.181564806037997</v>
       </c>
       <c r="B38">
-        <v>12.321180231018801</v>
+        <v>5.1142596398796796</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -1691,7 +1691,7 @@
         <v>46.177405710691097</v>
       </c>
       <c r="B39">
-        <v>10.974001707080101</v>
+        <v>4.45079947451379</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -1699,7 +1699,7 @@
         <v>60.986667010688798</v>
       </c>
       <c r="B40">
-        <v>8.9986827036674306</v>
+        <v>3.50763767785193</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -1707,7 +1707,7 @@
         <v>80.545312059649504</v>
       </c>
       <c r="B41">
-        <v>8.0161175482803895</v>
+        <v>3.0532115209401902</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -1715,7 +1715,7 @@
         <v>101.557361544042</v>
       </c>
       <c r="B42">
-        <v>7.0231319669424401</v>
+        <v>2.6051755574231001</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -1723,7 +1723,7 @@
         <v>128.05087496773299</v>
       </c>
       <c r="B43">
-        <v>5.8548375185376997</v>
+        <v>2.0941983670725</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -1731,7 +1731,7 @@
         <v>163.97026580002</v>
       </c>
       <c r="B44">
-        <v>4.96250728357934</v>
+        <v>1.71728109379733</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -1739,7 +1739,7 @@
         <v>200.45339809052399</v>
       </c>
       <c r="B45">
-        <v>4.2059424453194598</v>
+        <v>1.40810807991284</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -1747,7 +1747,7 @@
         <v>252.746158678173</v>
       </c>
       <c r="B46">
-        <v>3.5648526895771</v>
+        <v>1.15464879283106</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -1755,7 +1755,7 @@
         <v>313.79375436648297</v>
       </c>
       <c r="B47">
-        <v>3.0214248981853999</v>
+        <v>0.94679109481283696</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -1763,7 +1763,7 @@
         <v>383.612382741754</v>
       </c>
       <c r="B48">
-        <v>2.51871905259982</v>
+        <v>0.76105435036759905</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -1771,7 +1771,7 @@
         <v>476.26903780280003</v>
       </c>
       <c r="B49">
-        <v>2.1347643562690402</v>
+        <v>0.62405078156266502</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -1779,7 +1779,7 @@
         <v>619.364499097063</v>
       </c>
       <c r="B50">
-        <v>1.6656090700177399</v>
+        <v>0.46332708901377001</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -1787,7 +1787,7 @@
         <v>793.101660333307</v>
       </c>
       <c r="B51">
-        <v>1.41175517089725</v>
+        <v>0.37993671598539303</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -1795,7 +1795,7 @@
         <v>1015.57361544042</v>
       </c>
       <c r="B52">
-        <v>1.2165779526820599</v>
+        <v>0.31781027205944901</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -1803,7 +1803,7 @@
         <v>1241.53718500641</v>
       </c>
       <c r="B53">
-        <v>1.0836395413753299</v>
+        <v>0.27660613769186798</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -1811,7 +1811,7 @@
         <v>1589.7992284504701</v>
       </c>
       <c r="B54">
-        <v>0.88855162325931503</v>
+        <v>0.217981279532762</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -1819,7 +1819,7 @@
         <v>1973.7948588157701</v>
       </c>
       <c r="B55">
-        <v>0.74072778497987002</v>
+        <v>0.17522269779390801</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -1827,7 +1827,7 @@
         <v>2527.4615867817301</v>
       </c>
       <c r="B56">
-        <v>0.64898317042920795</v>
+        <v>0.149513401387046</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -1835,7 +1835,7 @@
         <v>3089.81790778802</v>
       </c>
       <c r="B57">
-        <v>0.55004168393631403</v>
+        <v>0.12259555486214301</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -1843,7 +1843,7 @@
         <v>3836.1238274175398</v>
       </c>
       <c r="B58">
-        <v>0.43630364384669601</v>
+        <v>9.2842453343758402E-2</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -1851,7 +1851,7 @@
         <v>4912.1901258538701</v>
       </c>
       <c r="B59">
-        <v>0.36980701916766401</v>
+        <v>7.6132515589664398E-2</v>
       </c>
     </row>
   </sheetData>
